--- a/驴酱杯对战信息_PIGFF队_vs_孙悟空队_BO1.xlsx
+++ b/驴酱杯对战信息_PIGFF队_vs_孙悟空队_BO1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE44905-9719-4BD1-92B2-CA614AAA5626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E02FDB-8BD5-40E9-B34A-5C2A52AB633B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30345" yWindow="2880" windowWidth="26715" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3405" yWindow="5085" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一局" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>2026-04-29 11:05</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>阵营</t>
   </si>
   <si>
@@ -295,6 +292,10 @@
   </si>
   <si>
     <t>奥术先驱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BV1fwoCBFEsD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -775,50 +776,50 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
         <v>52</v>
       </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -847,7 +848,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -876,63 +877,63 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -970,16 +971,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1017,16 +1018,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1064,16 +1065,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
         <v>58</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1111,16 +1112,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
         <v>60</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1158,16 +1159,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1205,16 +1206,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -1252,16 +1253,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -1299,16 +1300,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -1346,16 +1347,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
         <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1393,66 +1394,66 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
         <v>72</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>73</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>74</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>75</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>76</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>77</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>78</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>79</v>
-      </c>
-      <c r="J18" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
